--- a/suanli/源信网络算力补贴三方合作方案_配套表格.xlsx
+++ b/suanli/源信网络算力补贴三方合作方案_配套表格.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="准入与申请条件" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补贴标准表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补贴与优惠方式" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="各方职责分工" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="落地路径" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开放式可复制模式" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="火山引擎园区政策" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补贴与优惠方式" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="各方职责分工" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="落地路径" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开放式可复制模式" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +59,12 @@
       <i val="1"/>
       <color rgb="005A6472"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000B2A5B"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -114,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -137,6 +144,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -890,6 +898,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>二·补：火山引擎园区独立政策（已沟通确认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>政策一</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>无门槛·半年费用免费</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>按预估半年费用一次性发放代金券</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>园区企业 0 门槛即可享用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>政策二：大客户额外折扣（除代金券外，可叠加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>累计消费（万元）</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>额外折扣（除代金券外）</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>0 – 10</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>5 折 ～ 7 折</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>10 – 30</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>4.5 折 ～ 5 折</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>30 – 50</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4 折 ～ 4.5 折</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>折扣随累计</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>50 – 100</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>3.5 折 ～ 4 折</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>消费提升而</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>100 – 300</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>3 折 ～ 3.5 折</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>走低，越用</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>300 – 500 +</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>2.5 折 ～ 3 折</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>越优惠</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>说明：半年免费代金券与大客户额外折扣可叠加享受；具体折扣与额度以火山引擎最终政策为准。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -981,7 +1179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1112,7 +1310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1226,7 +1424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
